--- a/training_data/data_npd.xlsx
+++ b/training_data/data_npd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phillav/ECE 1390/Sheet-Music-Project/training_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771AD43A-9363-B549-B763-7CEF0A7C920A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F7521B-5004-084E-B39C-CC324DBF76B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="1220" windowWidth="26280" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="1040" windowWidth="26280" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>a3_1</t>
   </si>
@@ -250,16 +250,76 @@
   </si>
   <si>
     <t>rest_8</t>
+  </si>
+  <si>
+    <t>rest_9</t>
+  </si>
+  <si>
+    <t>rest_10</t>
+  </si>
+  <si>
+    <t>c3_9</t>
+  </si>
+  <si>
+    <t>d3_9</t>
+  </si>
+  <si>
+    <t>e3_9</t>
+  </si>
+  <si>
+    <t>f3_9</t>
+  </si>
+  <si>
+    <t>g3_9</t>
+  </si>
+  <si>
+    <t>a3_9</t>
+  </si>
+  <si>
+    <t>b3_9</t>
+  </si>
+  <si>
+    <t>c4_9</t>
+  </si>
+  <si>
+    <t>c3_10</t>
+  </si>
+  <si>
+    <t>d3_10</t>
+  </si>
+  <si>
+    <t>e3_10</t>
+  </si>
+  <si>
+    <t>f3_10</t>
+  </si>
+  <si>
+    <t>g3_10</t>
+  </si>
+  <si>
+    <t>a3_10</t>
+  </si>
+  <si>
+    <t>b3_10</t>
+  </si>
+  <si>
+    <t>c4_10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -567,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1287,10 +1347,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B66">
-        <v>6.7000000000000002E-3</v>
+        <v>130</v>
       </c>
       <c r="C66">
         <v>0.75</v>
@@ -1298,10 +1358,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B67">
-        <v>6.7000000000000002E-3</v>
+        <v>146</v>
       </c>
       <c r="C67">
         <v>0.75</v>
@@ -1309,10 +1369,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B68">
-        <v>6.7000000000000002E-3</v>
+        <v>164</v>
       </c>
       <c r="C68">
         <v>0.75</v>
@@ -1320,10 +1380,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B69">
-        <v>6.7000000000000002E-3</v>
+        <v>174</v>
       </c>
       <c r="C69">
         <v>0.75</v>
@@ -1331,10 +1391,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B70">
-        <v>6.7000000000000002E-3</v>
+        <v>196</v>
       </c>
       <c r="C70">
         <v>0.75</v>
@@ -1342,10 +1402,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B71">
-        <v>6.7000000000000002E-3</v>
+        <v>220</v>
       </c>
       <c r="C71">
         <v>0.75</v>
@@ -1353,10 +1413,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B72">
-        <v>6.7000000000000002E-3</v>
+        <v>246</v>
       </c>
       <c r="C72">
         <v>0.75</v>
@@ -1364,16 +1424,215 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73">
+        <v>261</v>
+      </c>
+      <c r="C73">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74">
+        <v>130</v>
+      </c>
+      <c r="C74">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75">
+        <v>146</v>
+      </c>
+      <c r="C75">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76">
+        <v>164</v>
+      </c>
+      <c r="C76">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77">
+        <v>174</v>
+      </c>
+      <c r="C77">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78">
+        <v>196</v>
+      </c>
+      <c r="C78">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>90</v>
+      </c>
+      <c r="B79">
+        <v>220</v>
+      </c>
+      <c r="C79">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>91</v>
+      </c>
+      <c r="B80">
+        <v>246</v>
+      </c>
+      <c r="C80">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81">
+        <v>261</v>
+      </c>
+      <c r="C81">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C82">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>68</v>
+      </c>
+      <c r="B83">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C83">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>69</v>
+      </c>
+      <c r="B84">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C84">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C85">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>71</v>
+      </c>
+      <c r="B86">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C86">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B87">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C87">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B88">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C88">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>74</v>
       </c>
-      <c r="B73">
+      <c r="B89">
         <v>6.7000000000000002E-3</v>
       </c>
-      <c r="C73">
+      <c r="C89">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>75</v>
+      </c>
+      <c r="B90">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C90">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>76</v>
+      </c>
+      <c r="B91">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C91">
         <v>0.75</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>